--- a/output/pdf_financials_xlsx/HI.xlsx
+++ b/output/pdf_financials_xlsx/HI.xlsx
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.00505</v>
       </c>
       <c r="F91" s="3" t="n">
         <v>0</v>
@@ -31903,7 +31903,11 @@
           <t>Translation reserve</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HI.xlsx
+++ b/output/pdf_financials_xlsx/HI.xlsx
@@ -963,10 +963,10 @@
         <v>0.129185</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.200877</v>
+        <v>0.680396</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.447692</v>
+        <v>2.997477</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001715</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000361</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006023</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -2117,13 +2117,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.559256</v>
+        <v>-0.560971</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.277635</v>
+        <v>-1.277996</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.332343</v>
+        <v>-1.338366</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.991562</v>
@@ -2245,13 +2245,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.559256</v>
+        <v>-0.560971</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.277635</v>
+        <v>-1.277996</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.331822</v>
+        <v>-1.337845</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.963448</v>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.33354</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.308925</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2576,13 +2576,13 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>6.240228</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.24271</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.042341</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.156382</v>
@@ -2597,10 +2597,10 @@
         <v>0.605046</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.164327</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.9826</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>12.929815</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.33354</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.308925</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2692,13 +2692,13 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>6.240228</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.24271</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.042341</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.156382</v>
@@ -2713,10 +2713,10 @@
         <v>0.605046</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.164327</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.9826</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>12.929815</v>
@@ -3376,10 +3376,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.362931</v>
+        <v>0.029391</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.38286</v>
+        <v>0.073935</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>1.609048</v>
@@ -3388,13 +3388,13 @@
         <v>16.045536</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.369449</v>
+        <v>0.129221</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.461622</v>
+        <v>0.218912</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.149278</v>
+        <v>0.106937</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.051849</v>
@@ -3409,10 +3409,10 @@
         <v>0.049666</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.200906</v>
+        <v>0.036579</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.02147</v>
+        <v>0.03887</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.121965</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -18499,7 +18499,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -29154,7 +29154,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -33210,7 +33210,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E249" s="5" t="n">
@@ -61496,7 +61496,7 @@
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -80467,7 +80467,7 @@
       </c>
       <c r="D720" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E720" t="inlineStr">
@@ -80481,10 +80481,10 @@
         </is>
       </c>
       <c r="G720" s="5" t="n">
-        <v>-0.680396</v>
+        <v>0.680396</v>
       </c>
       <c r="H720" s="5" t="n">
-        <v>-2.997477</v>
+        <v>2.997477</v>
       </c>
       <c r="I720" t="inlineStr">
         <is>
@@ -82380,7 +82380,7 @@
       </c>
       <c r="D739" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E739" s="5" t="n">

--- a/output/pdf_financials_xlsx/HI.xlsx
+++ b/output/pdf_financials_xlsx/HI.xlsx
@@ -765,10 +765,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.04728</v>
+        <v>0.150422</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.126222</v>
+        <v>0.363559</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.199303</v>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.048191</v>
+        <v>0.151333</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.129185</v>
+        <v>0.366522</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.680396</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.048191</v>
+        <v>-0.151333</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.129185</v>
+        <v>-0.366522</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -2570,10 +2570,10 @@
         <v>0.308925</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.204057</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>15.969645</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>6.240228</v>
@@ -2628,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>1.3053</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>0.308925</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.509357</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>15.969645</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>6.240228</v>
@@ -3382,10 +3382,10 @@
         <v>0.073935</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.609048</v>
+        <v>0.099691</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.045536</v>
+        <v>0.075891</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.129221</v>
@@ -3677,7 +3677,7 @@
         <v>0.000203</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0</v>
+        <v>0.133663</v>
       </c>
       <c r="F53" s="3" t="n">
         <v>0</v>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>1.331855</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>2.139232</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>4.509975</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>19.312032</v>
       </c>
       <c r="F88" s="3" t="n">
         <v>19.801726</v>
@@ -6020,16 +6020,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.499897</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.047897</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.078894</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.162095</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>3.609412</v>
@@ -30816,7 +30816,11 @@
           <t>Cash – Notes 5 $</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -30913,7 +30917,11 @@
           <t>Short-term investment – Note 5</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -31111,7 +31119,11 @@
           <t>Prepaid expenses – Note 10</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -31208,7 +31220,11 @@
           <t>Equipment – Note 6</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -31709,7 +31725,11 @@
           <t>Share capital – Note 8</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -31806,7 +31826,11 @@
           <t>Contributed surplus – Note 8</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -32309,7 +32333,11 @@
           <t>Cash and cash equivalents – Notes 3 and 6 $</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -32507,7 +32535,11 @@
           <t>Prepaid expenses – Notes 5 and 8</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -32709,7 +32741,11 @@
           <t>Mineral properties – Notes 4 and 8</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -32909,7 +32945,11 @@
           <t>Share capital – Note 5</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -33008,7 +33048,11 @@
           <t>Contributed surplus – Note 5</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -33410,7 +33454,11 @@
           <t>Prepaid expenses – Note 5</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E251" s="5" t="n">
         <v>0.002575</v>
       </c>
@@ -33509,7 +33557,11 @@
           <t>Mineral properties – Notes 3 and 4</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>MineralProperties</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>0.962936</v>
       </c>
@@ -33608,7 +33660,11 @@
           <t>Share capital – Note 4</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E253" s="5" t="n">
         <v>1.331855</v>
       </c>
@@ -33707,7 +33763,11 @@
           <t>Contributed surplus – Note 4</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>0.499897</v>
       </c>
@@ -81378,7 +81438,11 @@
           <t>Consulting fees – Note 6</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr"/>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E729" t="inlineStr">
         <is>
           <t>-</t>
@@ -81574,7 +81638,11 @@
           <t>Management fees – Note 6</t>
         </is>
       </c>
-      <c r="D731" t="inlineStr"/>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E731" t="inlineStr">
         <is>
           <t>-</t>
@@ -81774,7 +81842,11 @@
           <t>Rent – Note 6</t>
         </is>
       </c>
-      <c r="D733" t="inlineStr"/>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E733" t="inlineStr">
         <is>
           <t>-</t>
@@ -83378,7 +83450,11 @@
           <t>Consulting fees – Note 5</t>
         </is>
       </c>
-      <c r="D749" t="inlineStr"/>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E749" s="5" t="n">
         <v>0.036662</v>
       </c>
@@ -83477,7 +83553,11 @@
           <t>Management fees – Note 5</t>
         </is>
       </c>
-      <c r="D750" t="inlineStr"/>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E750" s="5" t="n">
         <v>0.035</v>
       </c>
@@ -83677,7 +83757,11 @@
           <t>Rent – Note 5</t>
         </is>
       </c>
-      <c r="D752" t="inlineStr"/>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E752" s="5" t="n">
         <v>0.03148</v>
       </c>

--- a/output/pdf_financials_xlsx/HI.xlsx
+++ b/output/pdf_financials_xlsx/HI.xlsx
@@ -6495,10 +6495,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.024723</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.041596</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -58435,7 +58435,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E500" t="inlineStr">
         <is>
           <t>-</t>
@@ -60152,7 +60156,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E517" s="5" t="n">
         <v>-0.024723</v>
       </c>
@@ -82753,7 +82761,11 @@
           <t>Future income tax recovery – Note 7</t>
         </is>
       </c>
-      <c r="D742" t="inlineStr"/>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E742" t="inlineStr">
         <is>
           <t>-</t>
@@ -84167,7 +84179,11 @@
           <t>Future income tax recovery – Note 6</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E756" t="inlineStr">
         <is>
           <t>-</t>
